--- a/project-a/tables/excel/CardTable.xlsx
+++ b/project-a/tables/excel/CardTable.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cards" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cards" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,10 +418,10 @@
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -550,7 +550,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slash</t>
+          <t>베기</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deal 6 damage.</t>
+          <t>피해 6을 줍니다.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>방어</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gain 7 block.</t>
+          <t>방어도 7을 얻습니다.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>집중</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Draw 1 card. Gain 1 energy.</t>
+          <t>카드 1장을 뽑고 에너지 1을 얻습니다.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Heavy Slash</t>
+          <t>강타</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deal 12 damage.</t>
+          <t>피해 12를 줍니다.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
